--- a/docs/package/05_Delivery/Upload_Templates/Scheme_Loan_Bookings_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Scheme_Loan_Bookings_Upload_Template.xlsx
@@ -447,7 +447,7 @@
     <t xml:space="preserve">Upload on</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Sales &amp; Marketing &gt; Scheme Issuance &gt; Upload loan bookings</t>
+    <t xml:space="preserve">Sales &amp; Placement &gt; Scheme Issuance &gt; Upload loan bookings</t>
   </si>
   <si>
     <t xml:space="preserve">File types</t>
